--- a/data/trending_integrated_20261023_15.xlsx
+++ b/data/trending_integrated_20261023_15.xlsx
@@ -578,13 +578,13 @@
         <v>-0.76</v>
       </c>
       <c r="E2" t="n">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="F2" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G2" t="n">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="H2" t="n">
         <v>2.67</v>
@@ -610,7 +610,7 @@
         <v>3.43</v>
       </c>
       <c r="O2" t="n">
-        <v>22284386779</v>
+        <v>22307274589</v>
       </c>
       <c r="P2" t="n">
         <v>8020</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1910</v>
+        <v>1939</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.82%</t>
+          <t>'+18.59%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.14</v>
       </c>
       <c r="E3" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F3" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G3" t="n">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="H3" t="n">
         <v>4.87</v>
@@ -702,7 +702,7 @@
         <v>5.01</v>
       </c>
       <c r="O3" t="n">
-        <v>80945264054</v>
+        <v>82448715989</v>
       </c>
       <c r="P3" t="n">
         <v>4980</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>59300</v>
+        <v>59450</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+7.04%</t>
+          <t>'+7.31%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>1.18</v>
       </c>
       <c r="E4" t="n">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="F4" t="n">
         <v>213</v>
       </c>
       <c r="G4" t="n">
-        <v>1229</v>
+        <v>1245</v>
       </c>
       <c r="H4" t="n">
         <v>38.9</v>
@@ -794,7 +794,7 @@
         <v>37.72</v>
       </c>
       <c r="O4" t="n">
-        <v>729099364050</v>
+        <v>739325938150</v>
       </c>
       <c r="P4" t="n">
         <v>67300</v>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1268500</v>
+        <v>1279000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+3.72%</t>
+          <t>'+4.58%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="G5" t="n">
-        <v>1961</v>
+        <v>2055</v>
       </c>
       <c r="H5" t="n">
         <v>48.77</v>
@@ -877,7 +877,7 @@
         <v>1200000</v>
       </c>
       <c r="L5" t="n">
-        <v>1275000</v>
+        <v>1280000</v>
       </c>
       <c r="M5" t="n">
         <v>1171000</v>
@@ -886,7 +886,7 @@
         <v>48.79</v>
       </c>
       <c r="O5" t="n">
-        <v>3789476120000</v>
+        <v>3939752216500</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>솔리다임 상장 철회 관련 호재성 언급 및 특별배당 기대. 13만원 이상 폭등 및 300만원 목표가 제시.</t>
+          <t>솔리다임 상장 철회 관련 호재로 인한 단기 급등 기대감 형성. 공매도 청산 및 자사주 매입 이슈 부각.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['솔리다임', '특별배당', '폭등']</t>
+          <t>['상장 철회', '호재', '공매도']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13810</v>
+        <v>13780</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+3.52%</t>
+          <t>'+3.30%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.5600000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="F6" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G6" t="n">
-        <v>617</v>
+        <v>705</v>
       </c>
       <c r="H6" t="n">
         <v>2.92</v>
@@ -969,7 +969,7 @@
         <v>12840</v>
       </c>
       <c r="L6" t="n">
-        <v>13880</v>
+        <v>13910</v>
       </c>
       <c r="M6" t="n">
         <v>12530</v>
@@ -978,7 +978,7 @@
         <v>3.48</v>
       </c>
       <c r="O6" t="n">
-        <v>73106294000</v>
+        <v>75873310175</v>
       </c>
       <c r="P6" t="n">
         <v>31500</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3790</v>
+        <v>3830</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+1.07%</t>
+          <t>'+2.13%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="F7" t="n">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="G7" t="n">
-        <v>1048</v>
+        <v>1061</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>165299457214</v>
+        <v>166113682006</v>
       </c>
       <c r="P7" t="n">
         <v>7050</v>
@@ -1130,13 +1130,13 @@
         <v>-0.06</v>
       </c>
       <c r="E8" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F8" t="n">
         <v>42</v>
       </c>
       <c r="G8" t="n">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="H8" t="n">
         <v>9.890000000000001</v>
@@ -1162,7 +1162,7 @@
         <v>9.949999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>32531846235</v>
+        <v>33404719005</v>
       </c>
       <c r="P8" t="n">
         <v>40350</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>3분기 실적 부진 및 의도적 주가 하락에 대한 의혹 제기. 거래량 감소와 함께 부정적 전망.</t>
+          <t>주가 조작 및 공매도 이슈에 대한 부정적 논조. 실적 발표 이후 주가 하락 및 반등 여부에 대한 관망세.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['실적', '주가 조작', '거래량']</t>
+          <t>['공매도', '주가조작']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8700</v>
+        <v>8690</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.23%</t>
+          <t>'+0.12%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.04</v>
       </c>
       <c r="E9" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F9" t="n">
         <v>56</v>
       </c>
       <c r="G9" t="n">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="H9" t="n">
         <v>5.11</v>
@@ -1254,7 +1254,7 @@
         <v>5.15</v>
       </c>
       <c r="O9" t="n">
-        <v>6952099295</v>
+        <v>6984066625</v>
       </c>
       <c r="P9" t="n">
         <v>15900</v>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>213750</v>
+        <v>214250</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.35%</t>
+          <t>'-0.12%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="G10" t="n">
-        <v>1747</v>
+        <v>1731</v>
       </c>
       <c r="H10" t="n">
         <v>46.13</v>
@@ -1346,7 +1346,7 @@
         <v>46.14</v>
       </c>
       <c r="O10" t="n">
-        <v>2823544092250</v>
+        <v>2901576167500</v>
       </c>
       <c r="P10" t="n">
         <v>374500</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>추세 전환 및 24만원 목표 전망. 나스닥 필라델피아 반도체주 동반 상승 기대.</t>
+          <t>추세 전환 기대감 속 개인 투자자 매수세 유입. 다만, 양전 시도를 막는 매물 출회 관찰.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['반도체주', '추세 전환', '목표가']</t>
+          <t>['추세', '매물']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7100</v>
+        <v>7110</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.80%</t>
+          <t>'-1.66%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F11" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G11" t="n">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="H11" t="n">
         <v>25.42</v>
@@ -1438,7 +1438,7 @@
         <v>25.47</v>
       </c>
       <c r="O11" t="n">
-        <v>15486551590</v>
+        <v>16233993145</v>
       </c>
       <c r="P11" t="n">
         <v>17950</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16940</v>
+        <v>16900</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-2.36%</t>
+          <t>'-2.59%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.48</v>
       </c>
       <c r="E12" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G12" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="H12" t="n">
         <v>3.77</v>
@@ -1530,7 +1530,7 @@
         <v>3.29</v>
       </c>
       <c r="O12" t="n">
-        <v>51489009770</v>
+        <v>51800602500</v>
       </c>
       <c r="P12" t="n">
         <v>22450</v>
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16800</v>
+        <v>16790</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.00%</t>
+          <t>'-3.06%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1593,10 +1593,10 @@
         <v>120</v>
       </c>
       <c r="F13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G13" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H13" t="n">
         <v>27.89</v>
@@ -1622,7 +1622,7 @@
         <v>27.87</v>
       </c>
       <c r="O13" t="n">
-        <v>38225183465</v>
+        <v>40251894605</v>
       </c>
       <c r="P13" t="n">
         <v>35350</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>59200</v>
+        <v>59100</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.90%</t>
+          <t>'-4.06%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="F14" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="G14" t="n">
-        <v>740</v>
+        <v>754</v>
       </c>
       <c r="H14" t="n">
         <v>22.25</v>
@@ -1714,7 +1714,7 @@
         <v>22.26</v>
       </c>
       <c r="O14" t="n">
-        <v>137155453450</v>
+        <v>141066669900</v>
       </c>
       <c r="P14" t="n">
         <v>139200</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>코스피 지수 및 미 증시 폭락과 연계하여 부정적 전망. 공매도 물량 및 최악의 종목으로 언급.</t>
+          <t>미국 증시 폭락 및 정치적 이슈에 따른 하락세 전망. 개별 종목 이슈보다는 거시 경제 및 정치적 요인에 대한 부정적 심리 우세.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['코스피', '미증시', '공매도']</t>
+          <t>['미증시', '정치']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9260</v>
+        <v>9270</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-8.23%</t>
+          <t>'-8.13%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-1.19</v>
       </c>
       <c r="E15" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F15" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G15" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="H15" t="n">
         <v>2.5</v>
@@ -1806,7 +1806,7 @@
         <v>3.69</v>
       </c>
       <c r="O15" t="n">
-        <v>50694768210</v>
+        <v>51455811810</v>
       </c>
       <c r="P15" t="n">
         <v>11690</v>

--- a/data/trending_integrated_20261023_15.xlsx
+++ b/data/trending_integrated_20261023_15.xlsx
@@ -578,13 +578,13 @@
         <v>-0.76</v>
       </c>
       <c r="E2" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F2" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="H2" t="n">
         <v>2.67</v>
@@ -610,7 +610,7 @@
         <v>3.43</v>
       </c>
       <c r="O2" t="n">
-        <v>22307274589</v>
+        <v>22369657459</v>
       </c>
       <c r="P2" t="n">
         <v>8020</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>오세훈 전 시장 무죄 판결에 따른 대권주자 관련 기대감 상승. 10배 상승 및 10연상 가능성 언급.</t>
+          <t>특정 정치인의 무죄 판결에 따른 기대감으로 주가 급등 가능성을 언급하나, 구체적인 근거는 부족함.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['대권주자', '무죄 판결', '텐버거']</t>
+          <t>['대권', '무죄', '텐버거']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1939</v>
+        <v>1921</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+18.59%</t>
+          <t>'+17.49%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.14</v>
       </c>
       <c r="E3" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F3" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G3" t="n">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="H3" t="n">
         <v>4.87</v>
@@ -702,7 +702,7 @@
         <v>5.01</v>
       </c>
       <c r="O3" t="n">
-        <v>82448715989</v>
+        <v>83555311170</v>
       </c>
       <c r="P3" t="n">
         <v>4980</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>59450</v>
+        <v>59700</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+7.31%</t>
+          <t>'+7.76%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>1.18</v>
       </c>
       <c r="E4" t="n">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="F4" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="G4" t="n">
-        <v>1245</v>
+        <v>1273</v>
       </c>
       <c r="H4" t="n">
         <v>38.9</v>
@@ -794,7 +794,7 @@
         <v>37.72</v>
       </c>
       <c r="O4" t="n">
-        <v>739325938150</v>
+        <v>746828824300</v>
       </c>
       <c r="P4" t="n">
         <v>67300</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>외인/기관 대규모 순매수 및 자사주 매입/소각 공시 기반 목표가 7만원 및 12~13만원 전망. MSCI 패시브 자금 유입 기대.</t>
+          <t>외인·기관의 대규모 매수 유입과 자사주 매입·소각 공시를 기반으로 한 주가 상승 전망이 우세함.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['자사주 매입', 'MSCI', '목표가']</t>
+          <t>['자사주 매입', '공시', ' MSCI']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1279000</v>
+        <v>1281000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+4.58%</t>
+          <t>'+4.74%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="G5" t="n">
-        <v>2055</v>
+        <v>2049</v>
       </c>
       <c r="H5" t="n">
         <v>48.77</v>
@@ -877,7 +877,7 @@
         <v>1200000</v>
       </c>
       <c r="L5" t="n">
-        <v>1280000</v>
+        <v>1284000</v>
       </c>
       <c r="M5" t="n">
         <v>1171000</v>
@@ -886,7 +886,7 @@
         <v>48.79</v>
       </c>
       <c r="O5" t="n">
-        <v>3939752216500</v>
+        <v>4052426269000</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>솔리다임 상장 철회 관련 호재로 인한 단기 급등 기대감 형성. 공매도 청산 및 자사주 매입 이슈 부각.</t>
+          <t>솔리다임 상장 철회 이슈가 긍정적 호재로 작용하며 주가 상승에 대한 기대감을 높이고 있음.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['상장 철회', '호재', '공매도']</t>
+          <t>['솔리다임', '상장 철회', '호재']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13780</v>
+        <v>13850</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+3.30%</t>
+          <t>'+3.82%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.5600000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F6" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G6" t="n">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="H6" t="n">
         <v>2.92</v>
@@ -978,7 +978,7 @@
         <v>3.48</v>
       </c>
       <c r="O6" t="n">
-        <v>75873310175</v>
+        <v>77209232460</v>
       </c>
       <c r="P6" t="n">
         <v>31500</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3830</v>
+        <v>3805</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+2.13%</t>
+          <t>'+1.47%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="F7" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G7" t="n">
-        <v>1061</v>
+        <v>1064</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>166113682006</v>
+        <v>166868594290</v>
       </c>
       <c r="P7" t="n">
         <v>7050</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14620</v>
+        <v>14640</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.62%</t>
+          <t>'+0.76%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.06</v>
       </c>
       <c r="E8" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F8" t="n">
         <v>42</v>
       </c>
       <c r="G8" t="n">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="H8" t="n">
         <v>9.890000000000001</v>
@@ -1162,7 +1162,7 @@
         <v>9.949999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>33404719005</v>
+        <v>35973111620</v>
       </c>
       <c r="P8" t="n">
         <v>40350</v>
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>신풍제약</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8690</v>
+        <v>215500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.12%</t>
+          <t>'+0.47%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>111</v>
+        <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>56</v>
+        <v>479</v>
       </c>
       <c r="G9" t="n">
-        <v>232</v>
+        <v>1770</v>
       </c>
       <c r="H9" t="n">
-        <v>5.11</v>
+        <v>46.13</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,91 +1239,91 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>8680</v>
+        <v>214500</v>
       </c>
       <c r="K9" t="n">
-        <v>9410</v>
+        <v>206000</v>
       </c>
       <c r="L9" t="n">
-        <v>9460</v>
+        <v>215500</v>
       </c>
       <c r="M9" t="n">
-        <v>8640</v>
+        <v>203500</v>
       </c>
       <c r="N9" t="n">
-        <v>5.15</v>
+        <v>46.14</v>
       </c>
       <c r="O9" t="n">
-        <v>6984066625</v>
+        <v>2995022268250</v>
       </c>
       <c r="P9" t="n">
-        <v>15900</v>
+        <v>374500</v>
       </c>
       <c r="Q9" t="n">
-        <v>6310</v>
+        <v>94500</v>
       </c>
       <c r="R9" t="n">
-        <v>-342000</v>
+        <v>-837000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>169000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>뇌졸중 치료제 관련 특허 보유 및 3상 성공 가능성 언급. 신약 개발 외자 유치 및 합병 기대감.</t>
+          <t>개인 투자자들의 매수세와 함께 주가 반등 기대감이 있으나, 특정 정치적 이슈 언급이 주된 내용임.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['뇌졸중치료제', '특허', '신약개발']</t>
+          <t>['평단', '양전', '추세']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>019170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>신풍제약</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>214250</v>
+        <v>8680</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.12%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>111</v>
       </c>
       <c r="F10" t="n">
-        <v>477</v>
+        <v>56</v>
       </c>
       <c r="G10" t="n">
-        <v>1731</v>
+        <v>232</v>
       </c>
       <c r="H10" t="n">
-        <v>46.13</v>
+        <v>5.11</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,60 +1331,60 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>214500</v>
+        <v>8680</v>
       </c>
       <c r="K10" t="n">
-        <v>206000</v>
+        <v>9410</v>
       </c>
       <c r="L10" t="n">
-        <v>215000</v>
+        <v>9460</v>
       </c>
       <c r="M10" t="n">
-        <v>203500</v>
+        <v>8640</v>
       </c>
       <c r="N10" t="n">
-        <v>46.14</v>
+        <v>5.15</v>
       </c>
       <c r="O10" t="n">
-        <v>2901576167500</v>
+        <v>7056299485</v>
       </c>
       <c r="P10" t="n">
-        <v>374500</v>
+        <v>15900</v>
       </c>
       <c r="Q10" t="n">
-        <v>94500</v>
+        <v>6310</v>
       </c>
       <c r="R10" t="n">
-        <v>-837000</v>
+        <v>-342000</v>
       </c>
       <c r="S10" t="n">
-        <v>169000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>추세 전환 기대감 속 개인 투자자 매수세 유입. 다만, 양전 시도를 막는 매물 출회 관찰.</t>
+          <t>뇌졸중 치료제 관련 특허 보유 및 3상 성공 가능성 언급. 신약 개발 외자 유치 및 합병 기대감.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['추세', '매물']</t>
+          <t>['뇌졸중치료제', '특허', '신약개발']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>019170</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7110</v>
+        <v>7130</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.66%</t>
+          <t>'-1.38%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F11" t="n">
         <v>69</v>
       </c>
       <c r="G11" t="n">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="H11" t="n">
         <v>25.42</v>
@@ -1438,7 +1438,7 @@
         <v>25.47</v>
       </c>
       <c r="O11" t="n">
-        <v>16233993145</v>
+        <v>16990690685</v>
       </c>
       <c r="P11" t="n">
         <v>17950</v>
@@ -1483,184 +1483,184 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B12" t="n">
+        <v>16810</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>'-2.94%</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E12" t="n">
+        <v>121</v>
+      </c>
+      <c r="F12" t="n">
+        <v>73</v>
+      </c>
+      <c r="G12" t="n">
+        <v>244</v>
+      </c>
+      <c r="H12" t="n">
+        <v>27.89</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>17320</v>
+      </c>
+      <c r="K12" t="n">
+        <v>16810</v>
+      </c>
+      <c r="L12" t="n">
         <v>16900</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>'-2.59%</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E12" t="n">
-        <v>99</v>
-      </c>
-      <c r="F12" t="n">
-        <v>57</v>
-      </c>
-      <c r="G12" t="n">
-        <v>146</v>
-      </c>
-      <c r="H12" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>MarketType.KOSDAQ</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>17350</v>
-      </c>
-      <c r="K12" t="n">
-        <v>18130</v>
-      </c>
-      <c r="L12" t="n">
-        <v>19070</v>
-      </c>
       <c r="M12" t="n">
-        <v>16530</v>
+        <v>16450</v>
       </c>
       <c r="N12" t="n">
-        <v>3.29</v>
+        <v>27.87</v>
       </c>
       <c r="O12" t="n">
-        <v>51800602500</v>
+        <v>41775487040</v>
       </c>
       <c r="P12" t="n">
-        <v>22450</v>
+        <v>35350</v>
       </c>
       <c r="Q12" t="n">
-        <v>6320</v>
+        <v>16450</v>
       </c>
       <c r="R12" t="n">
-        <v>-26000</v>
+        <v>238000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>34000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 보안주 폭등과 달리 국내 주가 흐름에 대한 불만이 제기되며, 위꼬리 음봉 패턴을 통한 물량 털어내기 의혹이 제기됨. AI 해킹 이슈와 보안주 상승 기대감이 있으나, 수급 부족 및 주가 조작 가능성에 대한 우려도 나타남.</t>
+          <t>조선주 전반의 하락세 및 신저점 기록. 주주 환원 정책 발표 가능성 언급 있으나 부정적 심리 우세.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['보안주', 'AI', '수급']</t>
+          <t>['조선주', '신저점', '주주환원']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16790</v>
+        <v>16820</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.06%</t>
+          <t>'-3.05%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.02</v>
+        <v>0.48</v>
       </c>
       <c r="E13" t="n">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="F13" t="n">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="G13" t="n">
-        <v>243</v>
+        <v>147</v>
       </c>
       <c r="H13" t="n">
-        <v>27.89</v>
+        <v>3.77</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>17320</v>
+        <v>17350</v>
       </c>
       <c r="K13" t="n">
-        <v>16810</v>
+        <v>18130</v>
       </c>
       <c r="L13" t="n">
-        <v>16900</v>
+        <v>19070</v>
       </c>
       <c r="M13" t="n">
-        <v>16450</v>
+        <v>16530</v>
       </c>
       <c r="N13" t="n">
-        <v>27.87</v>
+        <v>3.29</v>
       </c>
       <c r="O13" t="n">
-        <v>40251894605</v>
+        <v>52160523470</v>
       </c>
       <c r="P13" t="n">
-        <v>35350</v>
+        <v>22450</v>
       </c>
       <c r="Q13" t="n">
-        <v>16450</v>
+        <v>6320</v>
       </c>
       <c r="R13" t="n">
-        <v>238000</v>
+        <v>-26000</v>
       </c>
       <c r="S13" t="n">
-        <v>34000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>조선주 전반의 하락세 및 신저점 기록. 주주 환원 정책 발표 가능성 언급 있으나 부정적 심리 우세.</t>
+          <t>미국 보안주 폭등과 달리 국내 주가 흐름에 대한 불만이 제기되며, 위꼬리 음봉 패턴을 통한 물량 털어내기 의혹이 제기됨. AI 해킹 이슈와 보안주 상승 기대감이 있으나, 수급 부족 및 주가 조작 가능성에 대한 우려도 나타남.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['조선주', '신저점', '주주환원']</t>
+          <t>['보안주', 'AI', '수급']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
@@ -1682,13 +1682,13 @@
         <v>-0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="F14" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G14" t="n">
-        <v>754</v>
+        <v>778</v>
       </c>
       <c r="H14" t="n">
         <v>22.25</v>
@@ -1714,7 +1714,7 @@
         <v>22.26</v>
       </c>
       <c r="O14" t="n">
-        <v>141066669900</v>
+        <v>145187058550</v>
       </c>
       <c r="P14" t="n">
         <v>139200</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국 증시 폭락 및 정치적 이슈에 따른 하락세 전망. 개별 종목 이슈보다는 거시 경제 및 정치적 요인에 대한 부정적 심리 우세.</t>
+          <t>미국 증시 폭락 및 정치적 이슈에 대한 부정적 언급과 함께 주가 하락 및 부진에 대한 우려가 제기됨.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['미증시', '정치']</t>
+          <t>['개잡주', '폭락', '공매']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9270</v>
+        <v>9230</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-8.13%</t>
+          <t>'-8.52%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-1.19</v>
       </c>
       <c r="E15" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F15" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G15" t="n">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="H15" t="n">
         <v>2.5</v>
@@ -1806,7 +1806,7 @@
         <v>3.69</v>
       </c>
       <c r="O15" t="n">
-        <v>51455811810</v>
+        <v>52045209570</v>
       </c>
       <c r="P15" t="n">
         <v>11690</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>주가 급락 이후 조정 및 횡보를 예상하는 의견이 많으며, 일부에서는 시장 상황에 대한 부정적 언급과 함께 투매 및 하한가 가능성을 제기함.</t>
+          <t>최근 급락에 따른 주가 하락 및 횡보 가능성이 제기되며, 투자 심리가 위축된 상태임.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['주가 급락', '조정 예상', '투매']</t>
+          <t>['하한가', '급락', '횡보']</t>
         </is>
       </c>
       <c r="X15" t="n">

--- a/data/trending_integrated_20261023_15.xlsx
+++ b/data/trending_integrated_20261023_15.xlsx
@@ -578,13 +578,13 @@
         <v>-0.76</v>
       </c>
       <c r="E2" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F2" t="n">
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="H2" t="n">
         <v>2.67</v>
@@ -610,7 +610,7 @@
         <v>3.43</v>
       </c>
       <c r="O2" t="n">
-        <v>22369657459</v>
+        <v>22399347379</v>
       </c>
       <c r="P2" t="n">
         <v>8020</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>특정 정치인의 무죄 판결에 따른 기대감으로 주가 급등 가능성을 언급하나, 구체적인 근거는 부족함.</t>
+          <t>특정 인물의 무죄 판결과 관련된 기대감으로 급등 가능성 언급. 대권 관련 정치적 이슈와 연계하여 '10배', '10연상' 등 과도한 상승 예측.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['대권', '무죄', '텐버거']</t>
+          <t>['무죄', '대권', '상승']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1921</v>
+        <v>1944</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.49%</t>
+          <t>'+18.90%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.14</v>
       </c>
       <c r="E3" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="F3" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G3" t="n">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="H3" t="n">
         <v>4.87</v>
@@ -702,7 +702,7 @@
         <v>5.01</v>
       </c>
       <c r="O3" t="n">
-        <v>83555311170</v>
+        <v>84046820466</v>
       </c>
       <c r="P3" t="n">
         <v>4980</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>59700</v>
+        <v>59800</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+7.76%</t>
+          <t>'+7.94%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>1.18</v>
       </c>
       <c r="E4" t="n">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F4" t="n">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="G4" t="n">
-        <v>1273</v>
+        <v>1291</v>
       </c>
       <c r="H4" t="n">
         <v>38.9</v>
@@ -794,7 +794,7 @@
         <v>37.72</v>
       </c>
       <c r="O4" t="n">
-        <v>746828824300</v>
+        <v>754652398500</v>
       </c>
       <c r="P4" t="n">
         <v>67300</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>외인·기관의 대규모 매수 유입과 자사주 매입·소각 공시를 기반으로 한 주가 상승 전망이 우세함.</t>
+          <t>외인·기관의 대규모 순매수와 자사주 매입·소각 공시를 기반으로 한 상승 기대. MSCI 패시브 자금 유입 및 중동 특수 가능성 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['자사주 매입', '공시', ' MSCI']</t>
+          <t>['자사주 매입', 'MSCI', '외인']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1281000</v>
+        <v>1277000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+4.74%</t>
+          <t>'+4.42%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="G5" t="n">
-        <v>2049</v>
+        <v>2136</v>
       </c>
       <c r="H5" t="n">
         <v>48.77</v>
@@ -886,7 +886,7 @@
         <v>48.79</v>
       </c>
       <c r="O5" t="n">
-        <v>4052426269000</v>
+        <v>4423421586000</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>솔리다임 상장 철회 이슈가 긍정적 호재로 작용하며 주가 상승에 대한 기대감을 높이고 있음.</t>
+          <t>솔리다임 상장 철회 이슈를 호재로 인식하며 130 돌파 시 폭등 전망. 특별배당 및 공매도 청산 기대감도 존재.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['솔리다임', '상장 철회', '호재']</t>
+          <t>['솔리다임', '상장 철회', '공매도']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13850</v>
+        <v>13880</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+3.82%</t>
+          <t>'+4.05%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.5600000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F6" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G6" t="n">
-        <v>716</v>
+        <v>743</v>
       </c>
       <c r="H6" t="n">
         <v>2.92</v>
@@ -978,7 +978,7 @@
         <v>3.48</v>
       </c>
       <c r="O6" t="n">
-        <v>77209232460</v>
+        <v>77621149220</v>
       </c>
       <c r="P6" t="n">
         <v>31500</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3805</v>
+        <v>3810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+1.47%</t>
+          <t>'+1.60%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="F7" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G7" t="n">
-        <v>1064</v>
+        <v>1075</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>166868594290</v>
+        <v>167238819610</v>
       </c>
       <c r="P7" t="n">
         <v>7050</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14640</v>
+        <v>14700</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.76%</t>
+          <t>'+1.17%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.06</v>
       </c>
       <c r="E8" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="F8" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G8" t="n">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="H8" t="n">
         <v>9.890000000000001</v>
@@ -1162,7 +1162,7 @@
         <v>9.949999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>35973111620</v>
+        <v>36508853120</v>
       </c>
       <c r="P8" t="n">
         <v>40350</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>주가 조작 및 공매도 이슈에 대한 부정적 논조. 실적 발표 이후 주가 하락 및 반등 여부에 대한 관망세.</t>
+          <t>주가 조작 의혹과 연계된 부정적인 정치적 언급이 다수. 실적 발표 후 소폭 상승 기대감도 있으나 전반적인 하락 우려 존재.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['공매도', '주가조작']</t>
+          <t>['주가 조작', '공매', '실적']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="G9" t="n">
-        <v>1770</v>
+        <v>1842</v>
       </c>
       <c r="H9" t="n">
         <v>46.13</v>
@@ -1254,7 +1254,7 @@
         <v>46.14</v>
       </c>
       <c r="O9" t="n">
-        <v>2995022268250</v>
+        <v>3260455126750</v>
       </c>
       <c r="P9" t="n">
         <v>374500</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>개인 투자자들의 매수세와 함께 주가 반등 기대감이 있으나, 특정 정치적 이슈 언급이 주된 내용임.</t>
+          <t>추세 전환 기대감과 함께 22만, 24만원 상승 전망이 제기됨. 일부는 주가 하락을 막는 세력이 있다고 주장.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['평단', '양전', '추세']</t>
+          <t>['추세', '전망', '양전']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8680</v>
+        <v>8670</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'-0.12%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.04</v>
       </c>
       <c r="E10" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G10" t="n">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="H10" t="n">
         <v>5.11</v>
@@ -1346,7 +1346,7 @@
         <v>5.15</v>
       </c>
       <c r="O10" t="n">
-        <v>7056299485</v>
+        <v>7107990025</v>
       </c>
       <c r="P10" t="n">
         <v>15900</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7130</v>
+        <v>7150</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.38%</t>
+          <t>'-1.11%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F11" t="n">
         <v>69</v>
       </c>
       <c r="G11" t="n">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="H11" t="n">
         <v>25.42</v>
@@ -1438,7 +1438,7 @@
         <v>25.47</v>
       </c>
       <c r="O11" t="n">
-        <v>16990690685</v>
+        <v>18034905285</v>
       </c>
       <c r="P11" t="n">
         <v>17950</v>
@@ -1483,184 +1483,184 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16810</v>
+        <v>16900</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-2.94%</t>
+          <t>'-2.59%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.02</v>
+        <v>0.48</v>
       </c>
       <c r="E12" t="n">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="F12" t="n">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="G12" t="n">
-        <v>244</v>
+        <v>146</v>
       </c>
       <c r="H12" t="n">
-        <v>27.89</v>
+        <v>3.77</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>17320</v>
+        <v>17350</v>
       </c>
       <c r="K12" t="n">
-        <v>16810</v>
+        <v>18130</v>
       </c>
       <c r="L12" t="n">
-        <v>16900</v>
+        <v>19070</v>
       </c>
       <c r="M12" t="n">
-        <v>16450</v>
+        <v>16530</v>
       </c>
       <c r="N12" t="n">
-        <v>27.87</v>
+        <v>3.29</v>
       </c>
       <c r="O12" t="n">
-        <v>41775487040</v>
+        <v>52364337470</v>
       </c>
       <c r="P12" t="n">
-        <v>35350</v>
+        <v>22450</v>
       </c>
       <c r="Q12" t="n">
-        <v>16450</v>
+        <v>6320</v>
       </c>
       <c r="R12" t="n">
-        <v>238000</v>
+        <v>-26000</v>
       </c>
       <c r="S12" t="n">
-        <v>34000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>조선주 전반의 하락세 및 신저점 기록. 주주 환원 정책 발표 가능성 언급 있으나 부정적 심리 우세.</t>
+          <t>미국 보안주 폭등과 달리 국내 주가 흐름에 대한 불만이 제기되며, 위꼬리 음봉 패턴을 통한 물량 털어내기 의혹이 제기됨. AI 해킹 이슈와 보안주 상승 기대감이 있으나, 수급 부족 및 주가 조작 가능성에 대한 우려도 나타남.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['조선주', '신저점', '주주환원']</t>
+          <t>['보안주', 'AI', '수급']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16820</v>
+        <v>16830</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.05%</t>
+          <t>'-2.83%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.48</v>
+        <v>0.02</v>
       </c>
       <c r="E13" t="n">
-        <v>99</v>
+        <v>122</v>
       </c>
       <c r="F13" t="n">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="G13" t="n">
-        <v>147</v>
+        <v>247</v>
       </c>
       <c r="H13" t="n">
-        <v>3.77</v>
+        <v>27.89</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>17350</v>
+        <v>17320</v>
       </c>
       <c r="K13" t="n">
-        <v>18130</v>
+        <v>16810</v>
       </c>
       <c r="L13" t="n">
-        <v>19070</v>
+        <v>16900</v>
       </c>
       <c r="M13" t="n">
-        <v>16530</v>
+        <v>16450</v>
       </c>
       <c r="N13" t="n">
-        <v>3.29</v>
+        <v>27.87</v>
       </c>
       <c r="O13" t="n">
-        <v>52160523470</v>
+        <v>46234006490</v>
       </c>
       <c r="P13" t="n">
-        <v>22450</v>
+        <v>35350</v>
       </c>
       <c r="Q13" t="n">
-        <v>6320</v>
+        <v>16450</v>
       </c>
       <c r="R13" t="n">
-        <v>-26000</v>
+        <v>238000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>34000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 보안주 폭등과 달리 국내 주가 흐름에 대한 불만이 제기되며, 위꼬리 음봉 패턴을 통한 물량 털어내기 의혹이 제기됨. AI 해킹 이슈와 보안주 상승 기대감이 있으나, 수급 부족 및 주가 조작 가능성에 대한 우려도 나타남.</t>
+          <t>조선주 전반의 하락세 및 신저점 기록. 주주 환원 정책 발표 가능성 언급 있으나 부정적 심리 우세.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['보안주', 'AI', '수급']</t>
+          <t>['조선주', '신저점', '주주환원']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>59100</v>
+        <v>59400</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-4.06%</t>
+          <t>'-3.57%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1688,7 +1688,7 @@
         <v>176</v>
       </c>
       <c r="G14" t="n">
-        <v>778</v>
+        <v>839</v>
       </c>
       <c r="H14" t="n">
         <v>22.25</v>
@@ -1714,7 +1714,7 @@
         <v>22.26</v>
       </c>
       <c r="O14" t="n">
-        <v>145187058550</v>
+        <v>151115356750</v>
       </c>
       <c r="P14" t="n">
         <v>139200</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국 증시 폭락 및 정치적 이슈에 대한 부정적 언급과 함께 주가 하락 및 부진에 대한 우려가 제기됨.</t>
+          <t>정치적 이슈와 연계된 부정적 언급이 지배적. 미 증시 폭락에 따른 국내 증시 하락 및 개별 종목의 약세 전망.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['개잡주', '폭락', '공매']</t>
+          <t>['더불', '폭락', '개잡주']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9230</v>
+        <v>9210</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-8.52%</t>
+          <t>'-8.72%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-1.19</v>
       </c>
       <c r="E15" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F15" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G15" t="n">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="H15" t="n">
         <v>2.5</v>
@@ -1806,7 +1806,7 @@
         <v>3.69</v>
       </c>
       <c r="O15" t="n">
-        <v>52045209570</v>
+        <v>52519589040</v>
       </c>
       <c r="P15" t="n">
         <v>11690</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>최근 급락에 따른 주가 하락 및 횡보 가능성이 제기되며, 투자 심리가 위축된 상태임.</t>
+          <t>하락세 지속 및 조정·횡보 국면 예상. 브릴스 관련 뉴스 언급 있으나 전반적으로 투자 심리 위축 및 하한가 가능성 제기.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['하한가', '급락', '횡보']</t>
+          <t>['하한가', '조정', '횡보']</t>
         </is>
       </c>
       <c r="X15" t="n">

--- a/data/trending_integrated_20261023_15.xlsx
+++ b/data/trending_integrated_20261023_15.xlsx
@@ -578,13 +578,13 @@
         <v>-0.76</v>
       </c>
       <c r="E2" t="n">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="F2" t="n">
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="H2" t="n">
         <v>2.67</v>
@@ -610,7 +610,7 @@
         <v>3.43</v>
       </c>
       <c r="O2" t="n">
-        <v>22399347379</v>
+        <v>22403206849</v>
       </c>
       <c r="P2" t="n">
         <v>8020</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>특정 인물의 무죄 판결과 관련된 기대감으로 급등 가능성 언급. 대권 관련 정치적 이슈와 연계하여 '10배', '10연상' 등 과도한 상승 예측.</t>
+          <t>오세훈 전 시장 무죄 판결 관련 대권 기대감 및 상승 예상 언급. 근거는 정치적 이슈에 집중.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['무죄', '대권', '상승']</t>
+          <t>['진양산업', '오세훈', '대권']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>-0.14</v>
       </c>
       <c r="E3" t="n">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="F3" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="G3" t="n">
-        <v>294</v>
+        <v>310</v>
       </c>
       <c r="H3" t="n">
         <v>4.87</v>
@@ -702,7 +702,7 @@
         <v>5.01</v>
       </c>
       <c r="O3" t="n">
-        <v>84046820466</v>
+        <v>84066163266</v>
       </c>
       <c r="P3" t="n">
         <v>4980</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>휴머노이드 배터리 충전 상용화 및 CES 관련 로봇주 상승 기대. 외인 매수세 유입 및 물량 확보 움직임 관찰.</t>
+          <t>계속되는 주가 하락에 대한 우려와 함께 휴머노이드, 배터리 관련 기술 상용화 기대감 혼재. 외인 매수 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['휴머노이드', '로봇주', 'CES']</t>
+          <t>['앤로보틱스', '휴머노이드', '외인']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -762,13 +762,13 @@
         <v>1.18</v>
       </c>
       <c r="E4" t="n">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="F4" t="n">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G4" t="n">
-        <v>1291</v>
+        <v>1317</v>
       </c>
       <c r="H4" t="n">
         <v>38.9</v>
@@ -794,7 +794,7 @@
         <v>37.72</v>
       </c>
       <c r="O4" t="n">
-        <v>754652398500</v>
+        <v>755119974700</v>
       </c>
       <c r="P4" t="n">
         <v>67300</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>외인·기관의 대규모 순매수와 자사주 매입·소각 공시를 기반으로 한 상승 기대. MSCI 패시브 자금 유입 및 중동 특수 가능성 언급.</t>
+          <t>외인·기관 대규모 순매수, 자사주 매입 소각 공시 기반 상승 기대. MSCI 패시브 자금 유입 분석.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['자사주 매입', 'MSCI', '외인']</t>
+          <t>['삼성E&amp;A', '자사주 매입', 'MSCI']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="G5" t="n">
-        <v>2136</v>
+        <v>2181</v>
       </c>
       <c r="H5" t="n">
         <v>48.77</v>
@@ -886,7 +886,7 @@
         <v>48.79</v>
       </c>
       <c r="O5" t="n">
-        <v>4423421586000</v>
+        <v>4423963034000</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>솔리다임 상장 철회 이슈를 호재로 인식하며 130 돌파 시 폭등 전망. 특별배당 및 공매도 청산 기대감도 존재.</t>
+          <t>솔리다임 상장 철회에 따른 호재 인식 및 주가 상승 기대. 특별배당 발표 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['솔리다임', '상장 철회', '공매도']</t>
+          <t>['SK하이닉스', '솔리다임', '특별배당']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -946,13 +946,13 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F6" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G6" t="n">
-        <v>743</v>
+        <v>770</v>
       </c>
       <c r="H6" t="n">
         <v>2.92</v>
@@ -978,7 +978,7 @@
         <v>3.48</v>
       </c>
       <c r="O6" t="n">
-        <v>77621149220</v>
+        <v>77647396300</v>
       </c>
       <c r="P6" t="n">
         <v>31500</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>유리기판 관련 기술력과 삼성전자 인수합병 가능성에 대한 기대감이 높음. 광섬유 품귀 현상과 외인 매수세 유입에 따른 긍정적 전망이 제시되며, 미국 통신주 하락에도 불구하고 상승 가능성을 주장함.</t>
+          <t>유리기판 관련 기술 협업 및 특허 보유 사실 기반 상승 기대. 삼성 인수 가능성 및 EUV 기술 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['유리기판', '인수합병', '광섬유']</t>
+          <t>['대한광통신', '유리기판', 'EUV']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1038,13 +1038,13 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="F7" t="n">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="G7" t="n">
-        <v>1075</v>
+        <v>1153</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>167238819610</v>
+        <v>167268461410</v>
       </c>
       <c r="P7" t="n">
         <v>7050</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>북한 관련 이슈와 미 증시 변동성에 따른 방산주에 대한 관심이 높아지고 있으며, 일부 투자자들은 급등을 예상하고 있습니다.</t>
+          <t>북한 관련 지정학적 이슈에 따른 방산주 동반 상승 기대. 김정은 사망설 및 미국 정찰기 포착 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['북한', '방산주', '미 증시']</t>
+          <t>['빅텍', '북한', '방산주']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1130,13 +1130,13 @@
         <v>-0.06</v>
       </c>
       <c r="E8" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F8" t="n">
         <v>43</v>
       </c>
       <c r="G8" t="n">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="H8" t="n">
         <v>9.890000000000001</v>
@@ -1162,7 +1162,7 @@
         <v>9.949999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>36508853120</v>
+        <v>36520539620</v>
       </c>
       <c r="P8" t="n">
         <v>40350</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>주가 조작 의혹과 연계된 부정적인 정치적 언급이 다수. 실적 발표 후 소폭 상승 기대감도 있으나 전반적인 하락 우려 존재.</t>
+          <t>주가 조작 및 정치적 이슈에 대한 부정적 언급과 함께 실적 및 공매도 관련 논의. 종전회담 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['주가 조작', '공매', '실적']</t>
+          <t>['대우건설', '주가조작', '공매도']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="G9" t="n">
-        <v>1842</v>
+        <v>1839</v>
       </c>
       <c r="H9" t="n">
         <v>46.13</v>
@@ -1254,7 +1254,7 @@
         <v>46.14</v>
       </c>
       <c r="O9" t="n">
-        <v>3260455126750</v>
+        <v>3269156801250</v>
       </c>
       <c r="P9" t="n">
         <v>374500</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>추세 전환 기대감과 함께 22만, 24만원 상승 전망이 제기됨. 일부는 주가 하락을 막는 세력이 있다고 주장.</t>
+          <t>양전 시도 속 개인 물량 매도 관찰. 추세 전환 기대감과 정치 관련 언급 혼재.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['추세', '전망', '양전']</t>
+          <t>['삼성전자', '양전', '추세']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1320,7 +1320,7 @@
         <v>57</v>
       </c>
       <c r="G10" t="n">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="H10" t="n">
         <v>5.11</v>
@@ -1346,7 +1346,7 @@
         <v>5.15</v>
       </c>
       <c r="O10" t="n">
-        <v>7107990025</v>
+        <v>7108718305</v>
       </c>
       <c r="P10" t="n">
         <v>15900</v>
@@ -1406,13 +1406,13 @@
         <v>-0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F11" t="n">
         <v>69</v>
       </c>
       <c r="G11" t="n">
-        <v>561</v>
+        <v>574</v>
       </c>
       <c r="H11" t="n">
         <v>25.42</v>
@@ -1438,7 +1438,7 @@
         <v>25.47</v>
       </c>
       <c r="O11" t="n">
-        <v>18034905285</v>
+        <v>18043871385</v>
       </c>
       <c r="P11" t="n">
         <v>17950</v>
@@ -1530,7 +1530,7 @@
         <v>3.29</v>
       </c>
       <c r="O12" t="n">
-        <v>52364337470</v>
+        <v>52387574970</v>
       </c>
       <c r="P12" t="n">
         <v>22450</v>
@@ -1590,13 +1590,13 @@
         <v>0.02</v>
       </c>
       <c r="E13" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F13" t="n">
         <v>73</v>
       </c>
       <c r="G13" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H13" t="n">
         <v>27.89</v>
@@ -1622,7 +1622,7 @@
         <v>27.87</v>
       </c>
       <c r="O13" t="n">
-        <v>46234006490</v>
+        <v>46253630270</v>
       </c>
       <c r="P13" t="n">
         <v>35350</v>
@@ -1682,13 +1682,13 @@
         <v>-0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="F14" t="n">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="G14" t="n">
-        <v>839</v>
+        <v>849</v>
       </c>
       <c r="H14" t="n">
         <v>22.25</v>
@@ -1714,7 +1714,7 @@
         <v>22.26</v>
       </c>
       <c r="O14" t="n">
-        <v>151115356750</v>
+        <v>151117792150</v>
       </c>
       <c r="P14" t="n">
         <v>139200</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>정치적 이슈와 연계된 부정적 언급이 지배적. 미 증시 폭락에 따른 국내 증시 하락 및 개별 종목의 약세 전망.</t>
+          <t>미 증시 폭락 및 정치적 이슈와 연관된 부정적 전망. 개별 호재보다는 시장 상황 우려.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['더불', '폭락', '개잡주']</t>
+          <t>['두산에너빌리티', '미증시', '정치']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1774,13 +1774,13 @@
         <v>-1.19</v>
       </c>
       <c r="E15" t="n">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="F15" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G15" t="n">
-        <v>436</v>
+        <v>418</v>
       </c>
       <c r="H15" t="n">
         <v>2.5</v>
@@ -1806,7 +1806,7 @@
         <v>3.69</v>
       </c>
       <c r="O15" t="n">
-        <v>52519589040</v>
+        <v>52566210060</v>
       </c>
       <c r="P15" t="n">
         <v>11690</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>하락세 지속 및 조정·횡보 국면 예상. 브릴스 관련 뉴스 언급 있으나 전반적으로 투자 심리 위축 및 하한가 가능성 제기.</t>
+          <t>주가 하락 및 조정세에 대한 부정적 전망. 브릴스 AI 수출 실적 언급 있으나 전반적인 투심 악화.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['하한가', '조정', '횡보']</t>
+          <t>['HT로보틱스', '조정', 'AI']</t>
         </is>
       </c>
       <c r="X15" t="n">

--- a/data/trending_integrated_20261023_15.xlsx
+++ b/data/trending_integrated_20261023_15.xlsx
@@ -578,13 +578,13 @@
         <v>-0.76</v>
       </c>
       <c r="E2" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F2" t="n">
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="H2" t="n">
         <v>2.67</v>
@@ -610,7 +610,7 @@
         <v>3.43</v>
       </c>
       <c r="O2" t="n">
-        <v>22403206849</v>
+        <v>22403234299</v>
       </c>
       <c r="P2" t="n">
         <v>8020</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>오세훈 전 시장 무죄 판결 관련 대권 기대감 및 상승 예상 언급. 근거는 정치적 이슈에 집중.</t>
+          <t>정치권 무죄 판결에 따른 주가 급등 기대감 표출. 직접적인 호재 분석 부족.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['진양산업', '오세훈', '대권']</t>
+          <t>['무죄', '대선', '급등']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>-0.14</v>
       </c>
       <c r="E3" t="n">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="F3" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="G3" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H3" t="n">
         <v>4.87</v>
@@ -702,7 +702,7 @@
         <v>5.01</v>
       </c>
       <c r="O3" t="n">
-        <v>84066163266</v>
+        <v>84083608722</v>
       </c>
       <c r="P3" t="n">
         <v>4980</v>
@@ -765,10 +765,10 @@
         <v>439</v>
       </c>
       <c r="F4" t="n">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G4" t="n">
-        <v>1317</v>
+        <v>1345</v>
       </c>
       <c r="H4" t="n">
         <v>38.9</v>
@@ -794,7 +794,7 @@
         <v>37.72</v>
       </c>
       <c r="O4" t="n">
-        <v>755119974700</v>
+        <v>755185874300</v>
       </c>
       <c r="P4" t="n">
         <v>67300</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>외인·기관 대규모 순매수, 자사주 매입 소각 공시 기반 상승 기대. MSCI 패시브 자금 유입 분석.</t>
+          <t>외인/기관의 집중 매수와 자사주 매입/소각 공시에 따른 주가 상승 전망. MSCI 패시브 자금 유입 가능성 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['삼성E&amp;A', '자사주 매입', 'MSCI']</t>
+          <t>['자사주매입', '외국인', '공시']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="G5" t="n">
-        <v>2181</v>
+        <v>2228</v>
       </c>
       <c r="H5" t="n">
         <v>48.77</v>
@@ -886,7 +886,7 @@
         <v>48.79</v>
       </c>
       <c r="O5" t="n">
-        <v>4423963034000</v>
+        <v>4423966865000</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>솔리다임 상장 철회에 따른 호재 인식 및 주가 상승 기대. 특별배당 발표 언급.</t>
+          <t>솔리다임 상장 철회 뉴스를 호재로 인식하며 주가 상승 기대. 단기 급등 후 주주환원 정책에 대한 기대 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['SK하이닉스', '솔리다임', '특별배당']</t>
+          <t>['솔리다임', '상장철회', '주주환원']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -946,13 +946,13 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F6" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G6" t="n">
-        <v>770</v>
+        <v>788</v>
       </c>
       <c r="H6" t="n">
         <v>2.92</v>
@@ -978,7 +978,7 @@
         <v>3.48</v>
       </c>
       <c r="O6" t="n">
-        <v>77647396300</v>
+        <v>77662775340</v>
       </c>
       <c r="P6" t="n">
         <v>31500</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1038,13 +1038,13 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="F7" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G7" t="n">
-        <v>1153</v>
+        <v>1156</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>167268461410</v>
+        <v>167307266260</v>
       </c>
       <c r="P7" t="n">
         <v>7050</v>
@@ -1130,13 +1130,13 @@
         <v>-0.06</v>
       </c>
       <c r="E8" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F8" t="n">
         <v>43</v>
       </c>
       <c r="G8" t="n">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="H8" t="n">
         <v>9.890000000000001</v>
@@ -1162,7 +1162,7 @@
         <v>9.949999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>36520539620</v>
+        <v>36530109320</v>
       </c>
       <c r="P8" t="n">
         <v>40350</v>
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="G9" t="n">
-        <v>1839</v>
+        <v>1890</v>
       </c>
       <c r="H9" t="n">
         <v>46.13</v>
@@ -1254,7 +1254,7 @@
         <v>46.14</v>
       </c>
       <c r="O9" t="n">
-        <v>3269156801250</v>
+        <v>3271841500250</v>
       </c>
       <c r="P9" t="n">
         <v>374500</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>양전 시도 속 개인 물량 매도 관찰. 추세 전환 기대감과 정치 관련 언급 혼재.</t>
+          <t>단기 상승에 대한 기대와 함께 정치 관련 글에 대한 불만 표출. 외국인 수급 변화와 특별배당 기대 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['삼성전자', '양전', '추세']</t>
+          <t>['특별배당', '외국인', '컨콜']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1314,13 +1314,13 @@
         <v>-0.04</v>
       </c>
       <c r="E10" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F10" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G10" t="n">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="H10" t="n">
         <v>5.11</v>
@@ -1346,7 +1346,7 @@
         <v>5.15</v>
       </c>
       <c r="O10" t="n">
-        <v>7108718305</v>
+        <v>7110001465</v>
       </c>
       <c r="P10" t="n">
         <v>15900</v>
@@ -1406,13 +1406,13 @@
         <v>-0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="F11" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G11" t="n">
-        <v>574</v>
+        <v>586</v>
       </c>
       <c r="H11" t="n">
         <v>25.42</v>
@@ -1438,7 +1438,7 @@
         <v>25.47</v>
       </c>
       <c r="O11" t="n">
-        <v>18043871385</v>
+        <v>18048247185</v>
       </c>
       <c r="P11" t="n">
         <v>17950</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>3분기 호실적 및 재무 상태 개선, 과매도 구간 진입에 따른 반등 가능성에 대한 긍정적 분석과 함께, 목표가 하향 및 부채 관련 부정적 전망이 혼재함.</t>
+          <t>견조한 순이익 발표와 부채 감소에 따른 주가 재평가 기대. 목표가 하향 조정과 공매도 세력에 대한 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['3분기 실적', '재무 개선', '반등 가능성']</t>
+          <t>['순이익', '재무구조', '공매도']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1498,13 +1498,13 @@
         <v>0.48</v>
       </c>
       <c r="E12" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F12" t="n">
         <v>57</v>
       </c>
       <c r="G12" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H12" t="n">
         <v>3.77</v>
@@ -1530,7 +1530,7 @@
         <v>3.29</v>
       </c>
       <c r="O12" t="n">
-        <v>52387574970</v>
+        <v>52397765670</v>
       </c>
       <c r="P12" t="n">
         <v>22450</v>
@@ -1590,13 +1590,13 @@
         <v>0.02</v>
       </c>
       <c r="E13" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="F13" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G13" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="H13" t="n">
         <v>27.89</v>
@@ -1622,7 +1622,7 @@
         <v>27.87</v>
       </c>
       <c r="O13" t="n">
-        <v>46253630270</v>
+        <v>46254084680</v>
       </c>
       <c r="P13" t="n">
         <v>35350</v>
@@ -1682,13 +1682,13 @@
         <v>-0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F14" t="n">
         <v>181</v>
       </c>
       <c r="G14" t="n">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H14" t="n">
         <v>22.25</v>
@@ -1714,7 +1714,7 @@
         <v>22.26</v>
       </c>
       <c r="O14" t="n">
-        <v>151117792150</v>
+        <v>151118386150</v>
       </c>
       <c r="P14" t="n">
         <v>139200</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미 증시 폭락 및 정치적 이슈와 연관된 부정적 전망. 개별 호재보다는 시장 상황 우려.</t>
+          <t>정치적 이슈와 맞물려 주가 하락에 대한 부정적 전망. 공매도 물량 부담과 추후 반등 가능성 혼재.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['두산에너빌리티', '미증시', '정치']</t>
+          <t>['공매도', '하락', '반등']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1780,7 +1780,7 @@
         <v>76</v>
       </c>
       <c r="G15" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="H15" t="n">
         <v>2.5</v>
@@ -1806,7 +1806,7 @@
         <v>3.69</v>
       </c>
       <c r="O15" t="n">
-        <v>52566210060</v>
+        <v>52608281340</v>
       </c>
       <c r="P15" t="n">
         <v>11690</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>주가 하락 및 조정세에 대한 부정적 전망. 브릴스 AI 수출 실적 언급 있으나 전반적인 투심 악화.</t>
+          <t>주가 급락 후 조정 및 횡보 예상. AI 관련 사업 뉴스 언급에도 불구하고 부정적 전망 우세.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['HT로보틱스', '조정', 'AI']</t>
+          <t>['조정', '횡보', '급락']</t>
         </is>
       </c>
       <c r="X15" t="n">
